--- a/Module_1/data/2025Q2_data.xlsx
+++ b/Module_1/data/2025Q2_data.xlsx
@@ -5,6 +5,10 @@
   <sheets>
     <sheet state="visible" name="CONDENSED CONSOLIDATED BALANCE " sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="CONDENSED CONSOLIDATED STATEMEN" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet7" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="RECONCILIATION OF GAAP TO NON-G" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="FREE CASH FLOW" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="REMAINING PERFORMANCE OBLIGATIO" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="277">
   <si>
     <t>ASSETS</t>
   </si>
@@ -258,6 +262,591 @@
   </si>
   <si>
     <t>Weighted-average number of common shares used to compute net income (loss) per share attributable to common stockholders:</t>
+  </si>
+  <si>
+    <t>Revenue - subscription and transaction fees</t>
+  </si>
+  <si>
+    <t>Cost of revenue - service costs</t>
+  </si>
+  <si>
+    <t>Research and development</t>
+  </si>
+  <si>
+    <t>Sales and marketing</t>
+  </si>
+  <si>
+    <t>General and administrative</t>
+  </si>
+  <si>
+    <t>Total stock-based compensation</t>
+  </si>
+  <si>
+    <t>Cash flows from operating activities:</t>
+  </si>
+  <si>
+    <t>Adjustments to reconcile net income (loss) to net cash provided by operating activities:</t>
+  </si>
+  <si>
+    <t>Stock-based compensation</t>
+  </si>
+  <si>
+    <t>Amortization of intangible assets</t>
+  </si>
+  <si>
+    <t>Depreciation of property and equipment</t>
+  </si>
+  <si>
+    <t>Amortization of capitalized internal-use software costs paid in cash</t>
+  </si>
+  <si>
+    <t>Amortization of debt issuance costs</t>
+  </si>
+  <si>
+    <t>Accretion of discount on investments in marketable debt securities</t>
+  </si>
+  <si>
+    <t>(9,431</t>
+  </si>
+  <si>
+    <t>(11,078</t>
+  </si>
+  <si>
+    <t>(21,672</t>
+  </si>
+  <si>
+    <t>(24,171</t>
+  </si>
+  <si>
+    <t>Accretion of discount on loans held for investment</t>
+  </si>
+  <si>
+    <t>(5,329</t>
+  </si>
+  <si>
+    <t>(1,926</t>
+  </si>
+  <si>
+    <t>(9,960</t>
+  </si>
+  <si>
+    <t>(2,631</t>
+  </si>
+  <si>
+    <t>Gain on debt extinguishment</t>
+  </si>
+  <si>
+    <t>(40,472</t>
+  </si>
+  <si>
+    <t>(40,550</t>
+  </si>
+  <si>
+    <t>Provision for expected credit losses on acquired card receivables and other financial assets</t>
+  </si>
+  <si>
+    <t>Non-cash operating lease expense</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>(200</t>
+  </si>
+  <si>
+    <t>(100</t>
+  </si>
+  <si>
+    <t>Changes in assets and liabilities:</t>
+  </si>
+  <si>
+    <t>Accounts receivable</t>
+  </si>
+  <si>
+    <t>(3,317</t>
+  </si>
+  <si>
+    <t>(1,160</t>
+  </si>
+  <si>
+    <t>(26,164</t>
+  </si>
+  <si>
+    <t>(27,307</t>
+  </si>
+  <si>
+    <t>(151</t>
+  </si>
+  <si>
+    <t>(166</t>
+  </si>
+  <si>
+    <t>(1,240</t>
+  </si>
+  <si>
+    <t>(5,878</t>
+  </si>
+  <si>
+    <t>(2,074</t>
+  </si>
+  <si>
+    <t>(2,080</t>
+  </si>
+  <si>
+    <t>(2,494</t>
+  </si>
+  <si>
+    <t>(4,428</t>
+  </si>
+  <si>
+    <t>(4,917</t>
+  </si>
+  <si>
+    <t>(124</t>
+  </si>
+  <si>
+    <t>(15</t>
+  </si>
+  <si>
+    <t>(47</t>
+  </si>
+  <si>
+    <t>(2,788</t>
+  </si>
+  <si>
+    <t>(5,237</t>
+  </si>
+  <si>
+    <t>Net cash provided by operating activities</t>
+  </si>
+  <si>
+    <t>Cash flows from investing activities:</t>
+  </si>
+  <si>
+    <t>Purchases of corporate and customer fund short-term investments</t>
+  </si>
+  <si>
+    <t>(572,575</t>
+  </si>
+  <si>
+    <t>(590,652</t>
+  </si>
+  <si>
+    <t>(1,210,567</t>
+  </si>
+  <si>
+    <t>(990,240</t>
+  </si>
+  <si>
+    <t>Proceeds from maturities and sales of corporate and customer fund short-term investments</t>
+  </si>
+  <si>
+    <t>Purchase of intangible assets</t>
+  </si>
+  <si>
+    <t>(2,868</t>
+  </si>
+  <si>
+    <t>Purchases of loans held for investment</t>
+  </si>
+  <si>
+    <t>(198,987</t>
+  </si>
+  <si>
+    <t>(77,357</t>
+  </si>
+  <si>
+    <t>(380,673</t>
+  </si>
+  <si>
+    <t>(110,113</t>
+  </si>
+  <si>
+    <t>Principal repayments of loans held for investment</t>
+  </si>
+  <si>
+    <t>(12,342</t>
+  </si>
+  <si>
+    <t>Capitalization of internal-use software costs</t>
+  </si>
+  <si>
+    <t>(6,720</t>
+  </si>
+  <si>
+    <t>(5,117</t>
+  </si>
+  <si>
+    <t>(13,759</t>
+  </si>
+  <si>
+    <t>(10,762</t>
+  </si>
+  <si>
+    <t>(461</t>
+  </si>
+  <si>
+    <t>(352</t>
+  </si>
+  <si>
+    <t>(978</t>
+  </si>
+  <si>
+    <t>(755</t>
+  </si>
+  <si>
+    <t>Net cash provided by (used in) investing activities</t>
+  </si>
+  <si>
+    <t>(50,181</t>
+  </si>
+  <si>
+    <t>(129,696</t>
+  </si>
+  <si>
+    <t>Cash flows from financing activities:</t>
+  </si>
+  <si>
+    <t>Proceeds from issuance of convertible senior notes</t>
+  </si>
+  <si>
+    <t>Cash paid for convertible senior notes issuance costs</t>
+  </si>
+  <si>
+    <t>(23,100</t>
+  </si>
+  <si>
+    <t>Payments for repurchase of convertible senior notes</t>
+  </si>
+  <si>
+    <t>(539,403</t>
+  </si>
+  <si>
+    <t>Purchase of capped calls</t>
+  </si>
+  <si>
+    <t>(92,960</t>
+  </si>
+  <si>
+    <t>Customer fund deposits liability and other</t>
+  </si>
+  <si>
+    <t>(25,781</t>
+  </si>
+  <si>
+    <t>Prepaid card deposits</t>
+  </si>
+  <si>
+    <t>(2,505</t>
+  </si>
+  <si>
+    <t>(16,484</t>
+  </si>
+  <si>
+    <t>Repurchase of common stock</t>
+  </si>
+  <si>
+    <t>(199,999</t>
+  </si>
+  <si>
+    <t>(199,841</t>
+  </si>
+  <si>
+    <t>(400,001</t>
+  </si>
+  <si>
+    <t>(211,902</t>
+  </si>
+  <si>
+    <t>Proceeds from exercise of stock options</t>
+  </si>
+  <si>
+    <t>Tax withholdings related to net share settlements of equity awards</t>
+  </si>
+  <si>
+    <t>(3,410</t>
+  </si>
+  <si>
+    <t>(4,714</t>
+  </si>
+  <si>
+    <t>Proceeds from issuance of common stock under the employee stock purchase plan</t>
+  </si>
+  <si>
+    <t>Contingent consideration payout</t>
+  </si>
+  <si>
+    <t>(5,471</t>
+  </si>
+  <si>
+    <t>Net cash provided by financing activities</t>
+  </si>
+  <si>
+    <t>Effect of exchange rate changes on cash, cash equivalents, restricted cash and restricted cash equivalents</t>
+  </si>
+  <si>
+    <t>(645</t>
+  </si>
+  <si>
+    <t>(772</t>
+  </si>
+  <si>
+    <t>(7</t>
+  </si>
+  <si>
+    <t>Net increase in cash, cash equivalents, restricted cash, and restricted cash equivalents</t>
+  </si>
+  <si>
+    <t>Cash, cash equivalents, restricted cash, and restricted cash equivalents, beginning of period</t>
+  </si>
+  <si>
+    <t>Cash, cash equivalents, restricted cash, and restricted cash equivalents, end of period</t>
+  </si>
+  <si>
+    <t>Reconciliation of cash, cash equivalents, restricted cash, and restricted cash equivalents within the condensed consolidated balance sheets to the amounts shown in the condensed consolidated statements of cash flows above:</t>
+  </si>
+  <si>
+    <t>Restricted cash included in other current assets</t>
+  </si>
+  <si>
+    <t>Restricted cash included in other assets</t>
+  </si>
+  <si>
+    <t>Restricted cash and restricted cash equivalents included in funds held for customers</t>
+  </si>
+  <si>
+    <t>Total cash, cash equivalents, restricted cash, and restricted cash equivalents, end of period</t>
+  </si>
+  <si>
+    <t>Reconciliation of gross profit:</t>
+  </si>
+  <si>
+    <t>GAAP gross profit</t>
+  </si>
+  <si>
+    <t>Add:</t>
+  </si>
+  <si>
+    <t>Depreciation and amortization(1)</t>
+  </si>
+  <si>
+    <t>Stock-based compensation and related payroll taxes charged to cost of revenue</t>
+  </si>
+  <si>
+    <t>Non-GAAP gross profit</t>
+  </si>
+  <si>
+    <t>GAAP gross margin</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Non-GAAP gross margin</t>
+  </si>
+  <si>
+    <t>Reconciliation of operating expenses:</t>
+  </si>
+  <si>
+    <t>GAAP research and development expenses</t>
+  </si>
+  <si>
+    <t>Less - stock-based compensation and related payroll taxes</t>
+  </si>
+  <si>
+    <t>(29,774</t>
+  </si>
+  <si>
+    <t>(26,550</t>
+  </si>
+  <si>
+    <t>(53,750</t>
+  </si>
+  <si>
+    <t>(54,437</t>
+  </si>
+  <si>
+    <t>Non-GAAP research and development expenses</t>
+  </si>
+  <si>
+    <t>GAAP sales and marketing expenses</t>
+  </si>
+  <si>
+    <t>(10,656</t>
+  </si>
+  <si>
+    <t>(13,009</t>
+  </si>
+  <si>
+    <t>(21,550</t>
+  </si>
+  <si>
+    <t>(27,091</t>
+  </si>
+  <si>
+    <t>Non-GAAP sales and marketing expenses</t>
+  </si>
+  <si>
+    <t>GAAP general and administrative expenses(1)</t>
+  </si>
+  <si>
+    <t>Less:</t>
+  </si>
+  <si>
+    <t>Stock-based compensation and related payroll taxes</t>
+  </si>
+  <si>
+    <t>(23,264</t>
+  </si>
+  <si>
+    <t>(20,547</t>
+  </si>
+  <si>
+    <t>(40,982</t>
+  </si>
+  <si>
+    <t>(41,934</t>
+  </si>
+  <si>
+    <t>Acquisition and integration-related expenses</t>
+  </si>
+  <si>
+    <t>(872</t>
+  </si>
+  <si>
+    <t>(969</t>
+  </si>
+  <si>
+    <t>Non-GAAP general and administrative expenses</t>
+  </si>
+  <si>
+    <t>Reconciliation of operating loss:</t>
+  </si>
+  <si>
+    <t>GAAP operating loss</t>
+  </si>
+  <si>
+    <t>Stock-based compensation and related payroll taxes charged to cost of revenue and operating expenses</t>
+  </si>
+  <si>
+    <t>(92</t>
+  </si>
+  <si>
+    <t>Non-GAAP operating income</t>
+  </si>
+  <si>
+    <t>Reconciliation of net income (loss):</t>
+  </si>
+  <si>
+    <t>GAAP net income (loss)</t>
+  </si>
+  <si>
+    <t>Add - GAAP provision for income taxes</t>
+  </si>
+  <si>
+    <t>Income (loss) before taxes</t>
+  </si>
+  <si>
+    <t>Add (less):</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income before non-GAAP tax adjustments</t>
+  </si>
+  <si>
+    <t>Non-GAAP provision for income taxes(2)</t>
+  </si>
+  <si>
+    <t>(15,728</t>
+  </si>
+  <si>
+    <t>(14,997</t>
+  </si>
+  <si>
+    <t>(32,884</t>
+  </si>
+  <si>
+    <t>(27,885</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income</t>
+  </si>
+  <si>
+    <t>Reconciliation of net income (loss) per share attributable to common stockholders, basic and diluted:</t>
+  </si>
+  <si>
+    <t>GAAP net income (loss) per share attributable to common stockholders, basic and diluted</t>
+  </si>
+  <si>
+    <t>(0.36</t>
+  </si>
+  <si>
+    <t>(0.62</t>
+  </si>
+  <si>
+    <t>(0.39</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income before non-GAAP tax adjustments per share attributable to common stockholders, basic</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income before non-GAAP tax adjustments per share attributable to common stockholders, diluted</t>
+  </si>
+  <si>
+    <t>Less - Non-GAAP provision for income taxes</t>
+  </si>
+  <si>
+    <t>(0.15</t>
+  </si>
+  <si>
+    <t>(0.14</t>
+  </si>
+  <si>
+    <t>(0.32</t>
+  </si>
+  <si>
+    <t>(0.26</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income per share attributable to common stockholders, basic</t>
+  </si>
+  <si>
+    <t>Non-GAAP net income per share attributable to common stockholders, diluted</t>
+  </si>
+  <si>
+    <t>Shares used to compute GAAP and non-GAAP net income (loss) per share attributable to common stockholders, basic</t>
+  </si>
+  <si>
+    <t>Shares used to compute GAAP net income (loss) per share attributable to common stockholders, diluted</t>
+  </si>
+  <si>
+    <t>Shares used to compute non-GAAP net income per share attributable to common stockholders, diluted</t>
+  </si>
+  <si>
+    <t>Purchases of property and equipment</t>
+  </si>
+  <si>
+    <t>(382</t>
+  </si>
+  <si>
+    <t>(399</t>
+  </si>
+  <si>
+    <t>Free cash flow</t>
+  </si>
+  <si>
+    <t>Remaining performance obligations to be recognized as revenue:</t>
+  </si>
+  <si>
+    <t>Over the next 1 year</t>
+  </si>
+  <si>
+    <t>Between 1 to 2 years</t>
+  </si>
+  <si>
+    <t>Thereafter</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -267,7 +856,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mmmm d, yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -298,6 +887,12 @@
       <name val="Sohne"/>
     </font>
     <font/>
+    <font>
+      <i/>
+      <sz val="15.0"/>
+      <color rgb="FF2A3035"/>
+      <name val="Sohne"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -335,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="53">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -456,6 +1051,39 @@
       <alignment vertical="top"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -469,6 +1097,22 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1347,13 +1991,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:I1"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="G11:I11"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:I1"/>
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="C35:E35"/>
@@ -1377,7 +2021,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="39.75"/>
+    <col customWidth="1" min="1" max="1" width="143.5"/>
+    <col customWidth="1" min="2" max="2" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2250,18 +2895,237 @@
       <c r="P32" s="29"/>
     </row>
     <row r="33">
-      <c r="A33" s="29"/>
+      <c r="A33" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="10">
+        <v>608.0</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H33" s="10">
+        <v>486.0</v>
+      </c>
+      <c r="I33" s="12"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="L33" s="11">
+        <v>1135.0</v>
+      </c>
+      <c r="M33" s="12"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="10">
+        <v>856.0</v>
+      </c>
+      <c r="Q33" s="12"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="14">
+        <v>2579.0</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14">
+        <v>2388.0</v>
+      </c>
+      <c r="I34" s="13"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="14">
+        <v>4732.0</v>
+      </c>
+      <c r="M34" s="13"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="14">
+        <v>4934.0</v>
+      </c>
+      <c r="Q34" s="13"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="11">
+        <v>29270.0</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="11">
+        <v>26160.0</v>
+      </c>
+      <c r="I35" s="12"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="11">
+        <v>52903.0</v>
+      </c>
+      <c r="M35" s="12"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="11">
+        <v>53526.0</v>
+      </c>
+      <c r="Q35" s="12"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="14">
+        <v>10480.0</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="14">
+        <v>12789.0</v>
+      </c>
+      <c r="I36" s="13"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="14">
+        <v>21274.0</v>
+      </c>
+      <c r="M36" s="13"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="14">
+        <v>26674.0</v>
+      </c>
+      <c r="Q36" s="13"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="11">
+        <v>22943.0</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="11">
+        <v>20322.0</v>
+      </c>
+      <c r="I37" s="12"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="11">
+        <v>40497.0</v>
+      </c>
+      <c r="M37" s="12"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="11">
+        <v>41302.0</v>
+      </c>
+      <c r="Q37" s="12"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B38" s="13"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="16">
+        <v>3355.0</v>
+      </c>
+      <c r="I38" s="15"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M38" s="15"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="16">
+        <v>3355.0</v>
+      </c>
+      <c r="Q38" s="15"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="10"/>
+      <c r="C39" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="43">
+        <v>65880.0</v>
+      </c>
+      <c r="E39" s="44"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="H39" s="43">
+        <v>65500.0</v>
+      </c>
+      <c r="I39" s="44"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="L39" s="43">
+        <v>120541.0</v>
+      </c>
+      <c r="M39" s="44"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="P39" s="43">
+        <v>130647.0</v>
+      </c>
+      <c r="Q39" s="44"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="K1:Q1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="K3:M3"/>
     <mergeCell ref="O3:Q3"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="K1:Q1"/>
-    <mergeCell ref="C1:I1"/>
     <mergeCell ref="G25:I25"/>
     <mergeCell ref="K25:M25"/>
     <mergeCell ref="G26:I26"/>
@@ -2283,4 +3147,4149 @@
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="177.13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33"/>
+      <c r="B1" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="33">
+        <v>2024.0</v>
+      </c>
+      <c r="D2" s="35"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="33">
+        <v>2023.0</v>
+      </c>
+      <c r="H2" s="35"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="33">
+        <v>2024.0</v>
+      </c>
+      <c r="L2" s="35"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="33">
+        <v>2023.0</v>
+      </c>
+      <c r="P2" s="35"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="14">
+        <v>33548.0</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="14">
+        <v>42460.0</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14">
+        <v>65884.0</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14">
+        <v>65500.0</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14">
+        <v>120541.0</v>
+      </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="14">
+        <v>130647.0</v>
+      </c>
+      <c r="P6" s="13"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="12"/>
+      <c r="C7" s="11">
+        <v>14657.0</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11">
+        <v>20222.0</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="11">
+        <v>31595.0</v>
+      </c>
+      <c r="L7" s="12"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="11">
+        <v>40443.0</v>
+      </c>
+      <c r="P7" s="12"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14">
+        <v>3510.0</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14">
+        <v>3240.0</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="14">
+        <v>6679.0</v>
+      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="14">
+        <v>6958.0</v>
+      </c>
+      <c r="P8" s="13"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="11">
+        <v>3889.0</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11">
+        <v>2387.0</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="11">
+        <v>7833.0</v>
+      </c>
+      <c r="L9" s="12"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="11">
+        <v>3739.0</v>
+      </c>
+      <c r="P9" s="12"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14">
+        <v>1001.0</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14">
+        <v>1762.0</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="14">
+        <v>1896.0</v>
+      </c>
+      <c r="L10" s="13"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="14">
+        <v>3523.0</v>
+      </c>
+      <c r="P10" s="13"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="6"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="P12" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="12"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="12"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="14">
+        <v>21358.0</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="14">
+        <v>16288.0</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="14">
+        <v>42019.0</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="14">
+        <v>28689.0</v>
+      </c>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="11">
+        <v>2062.0</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11">
+        <v>2164.0</v>
+      </c>
+      <c r="H15" s="12"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="11">
+        <v>4107.0</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="11">
+        <v>4552.0</v>
+      </c>
+      <c r="P15" s="12"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="13"/>
+      <c r="C16" s="24">
+        <v>340.0</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="8"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="24">
+        <v>590.0</v>
+      </c>
+      <c r="L16" s="13"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="P16" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14">
+        <v>2868.0</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="8"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="L18" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="24">
+        <v>390.0</v>
+      </c>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="12"/>
+      <c r="C19" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="11">
+        <v>4553.0</v>
+      </c>
+      <c r="H19" s="12"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="P19" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14">
+        <v>2004.0</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="8"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="14">
+        <v>8914.0</v>
+      </c>
+      <c r="L20" s="13"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="P20" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="12"/>
+      <c r="C21" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="11">
+        <v>2741.0</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M21" s="6"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="10">
+        <v>233.0</v>
+      </c>
+      <c r="P21" s="12"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14">
+        <v>16926.0</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14">
+        <v>23230.0</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="14">
+        <v>7135.0</v>
+      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="14">
+        <v>20944.0</v>
+      </c>
+      <c r="P22" s="13"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="12"/>
+      <c r="C23" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I23" s="6"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="L23" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M23" s="6"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="P23" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M24" s="8"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="P24" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="17"/>
+      <c r="C25" s="38">
+        <v>147.0</v>
+      </c>
+      <c r="D25" s="17"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="H25" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="6"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="38">
+        <v>804.0</v>
+      </c>
+      <c r="L25" s="17"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="P25" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="16">
+        <v>78716.0</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="16">
+        <v>79682.0</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="16">
+        <v>167298.0</v>
+      </c>
+      <c r="L26" s="15"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="16">
+        <v>133342.0</v>
+      </c>
+      <c r="P26" s="15"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B28" s="13"/>
+      <c r="C28" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="D28" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="8"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="H28" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I28" s="8"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="L28" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" s="8"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="P28" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="11">
+        <v>539073.0</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="11">
+        <v>524336.0</v>
+      </c>
+      <c r="H29" s="12"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="11">
+        <v>1102750.0</v>
+      </c>
+      <c r="L29" s="12"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="11">
+        <v>1281505.0</v>
+      </c>
+      <c r="P29" s="12"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="13"/>
+      <c r="C30" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="8"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="13"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="L30" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M30" s="8"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P30" s="13"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="6"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M31" s="6"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="P31" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="14">
+        <v>197462.0</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="14">
+        <v>68970.0</v>
+      </c>
+      <c r="H32" s="13"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="14">
+        <v>369449.0</v>
+      </c>
+      <c r="L32" s="13"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="14">
+        <v>94300.0</v>
+      </c>
+      <c r="P32" s="13"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="12"/>
+      <c r="C33" s="11">
+        <v>54918.0</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="11">
+        <v>29991.0</v>
+      </c>
+      <c r="H33" s="12"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="11">
+        <v>6950.0</v>
+      </c>
+      <c r="L33" s="12"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="P33" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B34" s="13"/>
+      <c r="C34" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="H34" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="8"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="L34" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M34" s="8"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="P34" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B35" s="17"/>
+      <c r="C35" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="6"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="6"/>
+      <c r="J35" s="17"/>
+      <c r="K35" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="L35" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M35" s="6"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="P35" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="16">
+        <v>9842.0</v>
+      </c>
+      <c r="D36" s="15"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="I36" s="8"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="L36" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="M36" s="8"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="16">
+        <v>251593.0</v>
+      </c>
+      <c r="P36" s="15"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" s="12"/>
+      <c r="C39" s="11">
+        <v>1400000.0</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="12"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="11">
+        <v>1400000.0</v>
+      </c>
+      <c r="L39" s="12"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="P39" s="12"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="D40" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="8"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="L40" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M40" s="8"/>
+      <c r="N40" s="13"/>
+      <c r="O40" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P40" s="13"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="D41" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E41" s="6"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="12"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="L41" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M41" s="6"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="P41" s="12"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="8"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="L42" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M42" s="8"/>
+      <c r="N42" s="13"/>
+      <c r="O42" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P42" s="13"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="12"/>
+      <c r="C43" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="6"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="11">
+        <v>390960.0</v>
+      </c>
+      <c r="H43" s="12"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="11">
+        <v>52731.0</v>
+      </c>
+      <c r="L43" s="12"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="11">
+        <v>299770.0</v>
+      </c>
+      <c r="P43" s="12"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B44" s="13"/>
+      <c r="C44" s="14">
+        <v>21049.0</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I44" s="8"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="14">
+        <v>32371.0</v>
+      </c>
+      <c r="L44" s="13"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="P44" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B45" s="12"/>
+      <c r="C45" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="H45" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I45" s="6"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="L45" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M45" s="6"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="P45" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="13"/>
+      <c r="C46" s="14">
+        <v>1235.0</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="14">
+        <v>2106.0</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="13"/>
+      <c r="K46" s="14">
+        <v>2252.0</v>
+      </c>
+      <c r="L46" s="13"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="13"/>
+      <c r="O46" s="14">
+        <v>5052.0</v>
+      </c>
+      <c r="P46" s="13"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="12"/>
+      <c r="C47" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="12"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="L47" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M47" s="6"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="P47" s="12"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="13"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="13"/>
+      <c r="K48" s="14">
+        <v>5302.0</v>
+      </c>
+      <c r="L48" s="13"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="14">
+        <v>7846.0</v>
+      </c>
+      <c r="P48" s="13"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="17"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="17"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="38" t="s">
+        <v>186</v>
+      </c>
+      <c r="P49" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="16">
+        <v>537631.0</v>
+      </c>
+      <c r="D50" s="15"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="15"/>
+      <c r="G50" s="16">
+        <v>190720.0</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="15"/>
+      <c r="K50" s="16">
+        <v>432478.0</v>
+      </c>
+      <c r="L50" s="15"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="15"/>
+      <c r="O50" s="16">
+        <v>78811.0</v>
+      </c>
+      <c r="P50" s="15"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" s="17"/>
+      <c r="C51" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="D51" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="38">
+        <v>173.0</v>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="17"/>
+      <c r="K51" s="38" t="s">
+        <v>190</v>
+      </c>
+      <c r="L51" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M51" s="6"/>
+      <c r="N51" s="17"/>
+      <c r="O51" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="P51" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="14">
+        <v>625544.0</v>
+      </c>
+      <c r="D52" s="13"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="14">
+        <v>220394.0</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="14">
+        <v>469308.0</v>
+      </c>
+      <c r="L52" s="13"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="14">
+        <v>463739.0</v>
+      </c>
+      <c r="P52" s="13"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18">
+        <v>3195163.0</v>
+      </c>
+      <c r="D53" s="17"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="18">
+        <v>4468186.0</v>
+      </c>
+      <c r="H53" s="17"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="18">
+        <v>3351399.0</v>
+      </c>
+      <c r="L53" s="17"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="17"/>
+      <c r="O53" s="18">
+        <v>4224841.0</v>
+      </c>
+      <c r="P53" s="17"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="20">
+        <v>3820707.0</v>
+      </c>
+      <c r="D54" s="21"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="20">
+        <v>4688580.0</v>
+      </c>
+      <c r="H54" s="21"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="20">
+        <v>3820707.0</v>
+      </c>
+      <c r="L54" s="21"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="20">
+        <v>4688580.0</v>
+      </c>
+      <c r="P54" s="21"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="B55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="14">
+        <v>1566271.0</v>
+      </c>
+      <c r="D56" s="13"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G56" s="14">
+        <v>1579633.0</v>
+      </c>
+      <c r="H56" s="13"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K56" s="14">
+        <v>1566271.0</v>
+      </c>
+      <c r="L56" s="13"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O56" s="14">
+        <v>1579633.0</v>
+      </c>
+      <c r="P56" s="13"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B57" s="12"/>
+      <c r="C57" s="11">
+        <v>92613.0</v>
+      </c>
+      <c r="D57" s="12"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="11">
+        <v>103462.0</v>
+      </c>
+      <c r="H57" s="12"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="11">
+        <v>92613.0</v>
+      </c>
+      <c r="L57" s="12"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="11">
+        <v>103462.0</v>
+      </c>
+      <c r="P57" s="12"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="14">
+        <v>5297.0</v>
+      </c>
+      <c r="D58" s="13"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="14">
+        <v>7116.0</v>
+      </c>
+      <c r="H58" s="13"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="13"/>
+      <c r="K58" s="14">
+        <v>5297.0</v>
+      </c>
+      <c r="L58" s="13"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="14">
+        <v>7116.0</v>
+      </c>
+      <c r="P58" s="13"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18">
+        <v>2156526.0</v>
+      </c>
+      <c r="D59" s="17"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="18">
+        <v>2998369.0</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="18">
+        <v>2156526.0</v>
+      </c>
+      <c r="L59" s="17"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="17"/>
+      <c r="O59" s="18">
+        <v>2998369.0</v>
+      </c>
+      <c r="P59" s="17"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="20">
+        <v>3820707.0</v>
+      </c>
+      <c r="D60" s="21"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="20">
+        <v>4688580.0</v>
+      </c>
+      <c r="H60" s="21"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="20">
+        <v>3820707.0</v>
+      </c>
+      <c r="L60" s="21"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="20">
+        <v>4688580.0</v>
+      </c>
+      <c r="P60" s="21"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="N27:P27"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="F55:H55"/>
+    <mergeCell ref="J55:L55"/>
+    <mergeCell ref="N55:P55"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="N38:P38"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="89.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33"/>
+      <c r="B1" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="33">
+        <v>2024.0</v>
+      </c>
+      <c r="D2" s="35"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="33">
+        <v>2023.0</v>
+      </c>
+      <c r="H2" s="35"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="33">
+        <v>2024.0</v>
+      </c>
+      <c r="L2" s="35"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="33">
+        <v>2023.0</v>
+      </c>
+      <c r="P2" s="35"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="14">
+        <v>295946.0</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="14">
+        <v>260118.0</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" s="14">
+        <v>589701.0</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O4" s="14">
+        <v>509077.0</v>
+      </c>
+      <c r="P4" s="13"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="14">
+        <v>10310.0</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="14">
+        <v>11138.0</v>
+      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="14">
+        <v>21403.0</v>
+      </c>
+      <c r="L6" s="13"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="14">
+        <v>22260.0</v>
+      </c>
+      <c r="P6" s="13"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="17"/>
+      <c r="C7" s="18">
+        <v>2654.0</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="18">
+        <v>2446.0</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="18">
+        <v>4837.0</v>
+      </c>
+      <c r="L7" s="17"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="18">
+        <v>5074.0</v>
+      </c>
+      <c r="P7" s="17"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="20">
+        <v>308910.0</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="20">
+        <v>273702.0</v>
+      </c>
+      <c r="H8" s="21"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="20">
+        <v>615941.0</v>
+      </c>
+      <c r="L8" s="21"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="20">
+        <v>536411.0</v>
+      </c>
+      <c r="P8" s="21"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="12"/>
+      <c r="C9" s="47">
+        <v>81.6</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="47">
+        <v>81.7</v>
+      </c>
+      <c r="H9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="47">
+        <v>81.8</v>
+      </c>
+      <c r="L9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="M9" s="6"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="47">
+        <v>81.7</v>
+      </c>
+      <c r="P9" s="48" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="B10" s="13"/>
+      <c r="C10" s="50">
+        <v>85.2</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="50">
+        <v>85.9</v>
+      </c>
+      <c r="H10" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="50">
+        <v>85.4</v>
+      </c>
+      <c r="L10" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="M10" s="8"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="50">
+        <v>86.0</v>
+      </c>
+      <c r="P10" s="51" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="29"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="14">
+        <v>84784.0</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="14">
+        <v>86489.0</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="14">
+        <v>163469.0</v>
+      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="14">
+        <v>175552.0</v>
+      </c>
+      <c r="P14" s="13"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="17"/>
+      <c r="C15" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="6"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="6"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="P15" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="20">
+        <v>55010.0</v>
+      </c>
+      <c r="D16" s="21"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="20">
+        <v>59939.0</v>
+      </c>
+      <c r="H16" s="21"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K16" s="20">
+        <v>109719.0</v>
+      </c>
+      <c r="L16" s="21"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O16" s="20">
+        <v>121115.0</v>
+      </c>
+      <c r="P16" s="21"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="14">
+        <v>132534.0</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="14">
+        <v>118305.0</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K18" s="14">
+        <v>258856.0</v>
+      </c>
+      <c r="L18" s="13"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="14">
+        <v>236704.0</v>
+      </c>
+      <c r="P18" s="13"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="B19" s="17"/>
+      <c r="C19" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="6"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="L19" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="17"/>
+      <c r="O19" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="P19" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="20">
+        <v>121878.0</v>
+      </c>
+      <c r="D20" s="21"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="20">
+        <v>105296.0</v>
+      </c>
+      <c r="H20" s="21"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="20">
+        <v>237306.0</v>
+      </c>
+      <c r="L20" s="21"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="20">
+        <v>209613.0</v>
+      </c>
+      <c r="P20" s="21"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="14">
+        <v>71122.0</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="14">
+        <v>70053.0</v>
+      </c>
+      <c r="H22" s="13"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K22" s="14">
+        <v>137893.0</v>
+      </c>
+      <c r="L22" s="13"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="14">
+        <v>143304.0</v>
+      </c>
+      <c r="P22" s="13"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="8"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="H24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="L24" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M24" s="8"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="P24" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" s="12"/>
+      <c r="C25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="6"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="P25" s="27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="15"/>
+      <c r="C26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="26">
+        <v>92.0</v>
+      </c>
+      <c r="L26" s="15"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="15"/>
+      <c r="O26" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="15"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="43">
+        <v>47858.0</v>
+      </c>
+      <c r="D27" s="44"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="43">
+        <v>48634.0</v>
+      </c>
+      <c r="H27" s="44"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K27" s="43">
+        <v>97003.0</v>
+      </c>
+      <c r="L27" s="44"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="43">
+        <v>100401.0</v>
+      </c>
+      <c r="P27" s="44"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="29"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31" s="8"/>
+      <c r="F31" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="8"/>
+      <c r="J31" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K31" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L31" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M31" s="8"/>
+      <c r="N31" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O31" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="P31" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14">
+        <v>18168.0</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="14">
+        <v>23462.0</v>
+      </c>
+      <c r="H33" s="13"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="14">
+        <v>38274.0</v>
+      </c>
+      <c r="L33" s="13"/>
+      <c r="M33" s="8"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="14">
+        <v>47401.0</v>
+      </c>
+      <c r="P33" s="13"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" s="12"/>
+      <c r="C34" s="11">
+        <v>66348.0</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="11">
+        <v>62552.0</v>
+      </c>
+      <c r="H34" s="12"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="11">
+        <v>121119.0</v>
+      </c>
+      <c r="L34" s="12"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="11">
+        <v>128536.0</v>
+      </c>
+      <c r="P34" s="12"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B35" s="13"/>
+      <c r="C35" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="13"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="24">
+        <v>872.0</v>
+      </c>
+      <c r="H35" s="13"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="13"/>
+      <c r="M35" s="8"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="24">
+        <v>969.0</v>
+      </c>
+      <c r="P35" s="13"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="17"/>
+      <c r="C36" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="17"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="18">
+        <v>25091.0</v>
+      </c>
+      <c r="H36" s="17"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="17"/>
+      <c r="K36" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="L36" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M36" s="6"/>
+      <c r="N36" s="17"/>
+      <c r="O36" s="18">
+        <v>25091.0</v>
+      </c>
+      <c r="P36" s="17"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C37" s="20">
+        <v>62806.0</v>
+      </c>
+      <c r="D37" s="21"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G37" s="20">
+        <v>44303.0</v>
+      </c>
+      <c r="H37" s="21"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K37" s="20">
+        <v>129894.0</v>
+      </c>
+      <c r="L37" s="21"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O37" s="20">
+        <v>77677.0</v>
+      </c>
+      <c r="P37" s="21"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="29"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B41" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="14">
+        <v>33548.0</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="H41" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I41" s="8"/>
+      <c r="J41" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="14">
+        <v>42460.0</v>
+      </c>
+      <c r="L41" s="13"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="P41" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="B42" s="17"/>
+      <c r="C42" s="38">
+        <v>45.0</v>
+      </c>
+      <c r="D42" s="17"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="18">
+        <v>1666.0</v>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="18">
+        <v>1314.0</v>
+      </c>
+      <c r="L42" s="17"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="17"/>
+      <c r="O42" s="18">
+        <v>2189.0</v>
+      </c>
+      <c r="P42" s="17"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14">
+        <v>33593.0</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="H43" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I43" s="8"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="14">
+        <v>43774.0</v>
+      </c>
+      <c r="L43" s="13"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="P43" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14">
+        <v>18168.0</v>
+      </c>
+      <c r="D45" s="13"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="14">
+        <v>23462.0</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="14">
+        <v>38274.0</v>
+      </c>
+      <c r="L45" s="13"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="14">
+        <v>47401.0</v>
+      </c>
+      <c r="P45" s="13"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" s="12"/>
+      <c r="C46" s="11">
+        <v>66348.0</v>
+      </c>
+      <c r="D46" s="12"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="11">
+        <v>62552.0</v>
+      </c>
+      <c r="H46" s="12"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="11">
+        <v>121119.0</v>
+      </c>
+      <c r="L46" s="12"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="11">
+        <v>128536.0</v>
+      </c>
+      <c r="P46" s="12"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="13"/>
+      <c r="C47" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="24">
+        <v>872.0</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="13"/>
+      <c r="K47" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="13"/>
+      <c r="M47" s="8"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="24">
+        <v>969.0</v>
+      </c>
+      <c r="P47" s="13"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="12"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="11">
+        <v>25091.0</v>
+      </c>
+      <c r="H48" s="12"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="L48" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="M48" s="6"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="11">
+        <v>25091.0</v>
+      </c>
+      <c r="P48" s="12"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="8"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="13"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="13"/>
+      <c r="K49" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="L49" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M49" s="8"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P49" s="13"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18">
+        <v>1001.0</v>
+      </c>
+      <c r="D50" s="17"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="18">
+        <v>1762.0</v>
+      </c>
+      <c r="H50" s="17"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="18">
+        <v>1896.0</v>
+      </c>
+      <c r="L50" s="17"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="17"/>
+      <c r="O50" s="18">
+        <v>3523.0</v>
+      </c>
+      <c r="P50" s="17"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14">
+        <v>78638.0</v>
+      </c>
+      <c r="D51" s="13"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="14">
+        <v>74984.0</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="14">
+        <v>164421.0</v>
+      </c>
+      <c r="L51" s="13"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="14">
+        <v>139427.0</v>
+      </c>
+      <c r="P51" s="13"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="B52" s="17"/>
+      <c r="C52" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="D52" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="6"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="38" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I52" s="6"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="38" t="s">
+        <v>248</v>
+      </c>
+      <c r="L52" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M52" s="6"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="38" t="s">
+        <v>249</v>
+      </c>
+      <c r="P52" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="20">
+        <v>62910.0</v>
+      </c>
+      <c r="D53" s="21"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G53" s="20">
+        <v>59987.0</v>
+      </c>
+      <c r="H53" s="21"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K53" s="20">
+        <v>131537.0</v>
+      </c>
+      <c r="L53" s="21"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O53" s="20">
+        <v>111542.0</v>
+      </c>
+      <c r="P53" s="21"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="29"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="24">
+        <v>0.33</v>
+      </c>
+      <c r="D57" s="13"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="H57" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I57" s="8"/>
+      <c r="J57" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="24">
+        <v>0.41</v>
+      </c>
+      <c r="L57" s="13"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P57" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="38">
+        <v>0.0</v>
+      </c>
+      <c r="D58" s="17"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="38">
+        <v>0.02</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="L58" s="17"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="38">
+        <v>0.02</v>
+      </c>
+      <c r="P58" s="17"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="24">
+        <v>0.33</v>
+      </c>
+      <c r="D59" s="13"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="H59" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I59" s="8"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="24">
+        <v>0.42</v>
+      </c>
+      <c r="L59" s="13"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="P59" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B61" s="13"/>
+      <c r="C61" s="24">
+        <v>0.18</v>
+      </c>
+      <c r="D61" s="13"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="24">
+        <v>0.21</v>
+      </c>
+      <c r="H61" s="13"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="24">
+        <v>0.37</v>
+      </c>
+      <c r="L61" s="13"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="24">
+        <v>0.45</v>
+      </c>
+      <c r="P61" s="13"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="D62" s="12"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="10">
+        <v>0.59</v>
+      </c>
+      <c r="H62" s="12"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="10">
+        <v>1.16</v>
+      </c>
+      <c r="L62" s="12"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="10">
+        <v>1.2</v>
+      </c>
+      <c r="P62" s="12"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="13"/>
+      <c r="C63" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="13"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="13"/>
+      <c r="G63" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="H63" s="13"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="13"/>
+      <c r="K63" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="13"/>
+      <c r="M63" s="8"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="24">
+        <v>0.01</v>
+      </c>
+      <c r="P63" s="13"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="12"/>
+      <c r="C64" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="12"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="H64" s="12"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="12"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="P64" s="12"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="8"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H65" s="13"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="L65" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M65" s="8"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="P65" s="13"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B66" s="17"/>
+      <c r="C66" s="38">
+        <v>0.01</v>
+      </c>
+      <c r="D66" s="17"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="38">
+        <v>0.02</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="17"/>
+      <c r="K66" s="38">
+        <v>0.02</v>
+      </c>
+      <c r="L66" s="17"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="17"/>
+      <c r="O66" s="38">
+        <v>0.03</v>
+      </c>
+      <c r="P66" s="17"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C67" s="19">
+        <v>0.76</v>
+      </c>
+      <c r="D67" s="21"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G67" s="19">
+        <v>0.71</v>
+      </c>
+      <c r="H67" s="21"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K67" s="19">
+        <v>1.58</v>
+      </c>
+      <c r="L67" s="21"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O67" s="19">
+        <v>1.31</v>
+      </c>
+      <c r="P67" s="21"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B68" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C68" s="42">
+        <v>0.7</v>
+      </c>
+      <c r="D68" s="44"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="G68" s="42">
+        <v>0.64</v>
+      </c>
+      <c r="H68" s="44"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K68" s="42">
+        <v>1.48</v>
+      </c>
+      <c r="L68" s="44"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="O68" s="42">
+        <v>1.19</v>
+      </c>
+      <c r="P68" s="44"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="15"/>
+      <c r="C69" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="D69" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="26" t="s">
+        <v>260</v>
+      </c>
+      <c r="H69" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="I69" s="8"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="L69" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="M69" s="8"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="P69" s="28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="B70" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="42">
+        <v>0.61</v>
+      </c>
+      <c r="D70" s="44"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="G70" s="42">
+        <v>0.57</v>
+      </c>
+      <c r="H70" s="44"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="K70" s="42">
+        <v>1.26</v>
+      </c>
+      <c r="L70" s="44"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="O70" s="42">
+        <v>1.05</v>
+      </c>
+      <c r="P70" s="44"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71" s="19">
+        <v>0.56</v>
+      </c>
+      <c r="D71" s="21"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G71" s="19">
+        <v>0.51</v>
+      </c>
+      <c r="H71" s="21"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K71" s="19">
+        <v>1.19</v>
+      </c>
+      <c r="L71" s="21"/>
+      <c r="M71" s="8"/>
+      <c r="N71" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O71" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="P71" s="21"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="41"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
+      <c r="D72" s="29"/>
+      <c r="E72" s="29"/>
+      <c r="F72" s="29"/>
+      <c r="G72" s="29"/>
+      <c r="H72" s="29"/>
+      <c r="I72" s="29"/>
+      <c r="J72" s="29"/>
+      <c r="K72" s="29"/>
+      <c r="L72" s="29"/>
+      <c r="M72" s="29"/>
+      <c r="N72" s="29"/>
+      <c r="O72" s="29"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="29"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="B74" s="12"/>
+      <c r="C74" s="11">
+        <v>103102.0</v>
+      </c>
+      <c r="D74" s="12"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="11">
+        <v>105914.0</v>
+      </c>
+      <c r="H74" s="12"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="11">
+        <v>104394.0</v>
+      </c>
+      <c r="L74" s="12"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="11">
+        <v>106350.0</v>
+      </c>
+      <c r="P74" s="12"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="B75" s="13"/>
+      <c r="C75" s="14">
+        <v>104480.0</v>
+      </c>
+      <c r="D75" s="13"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="13"/>
+      <c r="G75" s="14">
+        <v>105914.0</v>
+      </c>
+      <c r="H75" s="13"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="13"/>
+      <c r="K75" s="14">
+        <v>107718.0</v>
+      </c>
+      <c r="L75" s="13"/>
+      <c r="M75" s="8"/>
+      <c r="N75" s="13"/>
+      <c r="O75" s="14">
+        <v>106350.0</v>
+      </c>
+      <c r="P75" s="13"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B76" s="12"/>
+      <c r="C76" s="11">
+        <v>111919.0</v>
+      </c>
+      <c r="D76" s="12"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="11">
+        <v>116712.0</v>
+      </c>
+      <c r="H76" s="12"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="11">
+        <v>110840.0</v>
+      </c>
+      <c r="L76" s="12"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="11">
+        <v>117471.0</v>
+      </c>
+      <c r="P76" s="12"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="29"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="29"/>
+      <c r="F77" s="29"/>
+      <c r="G77" s="29"/>
+      <c r="H77" s="29"/>
+      <c r="I77" s="29"/>
+      <c r="J77" s="29"/>
+      <c r="K77" s="29"/>
+      <c r="L77" s="29"/>
+      <c r="M77" s="29"/>
+      <c r="N77" s="29"/>
+      <c r="O77" s="29"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="50">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="N40:P40"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="N44:P44"/>
+    <mergeCell ref="F60:H60"/>
+    <mergeCell ref="J60:L60"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="J56:L56"/>
+    <mergeCell ref="N56:P56"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="N60:P60"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="49.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="33"/>
+      <c r="B1" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="33">
+        <v>2024.0</v>
+      </c>
+      <c r="D2" s="35"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="33">
+        <v>2023.0</v>
+      </c>
+      <c r="H2" s="35"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="33">
+        <v>2024.0</v>
+      </c>
+      <c r="L2" s="35"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="33">
+        <v>2023.0</v>
+      </c>
+      <c r="P2" s="35"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="11">
+        <v>78716.0</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="11">
+        <v>79682.0</v>
+      </c>
+      <c r="H3" s="12"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="11">
+        <v>167298.0</v>
+      </c>
+      <c r="L3" s="12"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="11">
+        <v>133342.0</v>
+      </c>
+      <c r="P3" s="12"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="13"/>
+      <c r="C4" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="8"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="P4" s="36" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="H5" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="L5" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="P5" s="45" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="20">
+        <v>71614.0</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="20">
+        <v>74213.0</v>
+      </c>
+      <c r="H6" s="21"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="20">
+        <v>153140.0</v>
+      </c>
+      <c r="L6" s="21"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="20">
+        <v>121825.0</v>
+      </c>
+      <c r="P6" s="21"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="J1:P1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="73.25"/>
+    <col customWidth="1" min="3" max="3" width="23.5"/>
+    <col customWidth="1" min="7" max="7" width="17.25"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="52">
+        <v>45657.0</v>
+      </c>
+      <c r="D2" s="8"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52">
+        <v>45473.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="14">
+        <v>30464.0</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="14">
+        <v>30225.0</v>
+      </c>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="11">
+        <v>16700.0</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="11">
+        <v>16887.0</v>
+      </c>
+      <c r="H5" s="12"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="15"/>
+      <c r="C6" s="16">
+        <v>30882.0</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16">
+        <v>39733.0</v>
+      </c>
+      <c r="H6" s="15"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="43">
+        <v>78046.0</v>
+      </c>
+      <c r="D7" s="44"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="42" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="43">
+        <v>86845.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F3:H3"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>